--- a/research/traditional_assets/database/data/spain/spain_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_insurance_general.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.002700000000000001</v>
+        <v>0.00535</v>
       </c>
       <c r="E2">
-        <v>0.0228</v>
+        <v>0.0551</v>
       </c>
       <c r="F2">
-        <v>0.07870000000000001</v>
+        <v>0.0471</v>
       </c>
       <c r="G2">
-        <v>0.08846446043799157</v>
+        <v>0.1023582416690344</v>
       </c>
       <c r="H2">
-        <v>0.08846446043799157</v>
+        <v>0.1023582416690344</v>
       </c>
       <c r="I2">
-        <v>0.08589123352924991</v>
+        <v>0.0876697768756944</v>
       </c>
       <c r="J2">
-        <v>0.06583821440256776</v>
+        <v>0.06755857785238377</v>
       </c>
       <c r="K2">
-        <v>1166.4</v>
+        <v>1206.4</v>
       </c>
       <c r="L2">
-        <v>0.04280822546252629</v>
+        <v>0.04896700085237651</v>
       </c>
       <c r="M2">
-        <v>481.821</v>
+        <v>555.8939</v>
       </c>
       <c r="N2">
-        <v>0.04704594053605429</v>
+        <v>0.05765876300422152</v>
       </c>
       <c r="O2">
-        <v>0.4130838477366255</v>
+        <v>0.4607873839522547</v>
       </c>
       <c r="P2">
-        <v>481.821</v>
+        <v>555.8939</v>
       </c>
       <c r="Q2">
-        <v>0.04704594053605429</v>
+        <v>0.05765876300422152</v>
       </c>
       <c r="R2">
-        <v>0.4130838477366255</v>
+        <v>0.4607873839522547</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4782.8</v>
+        <v>4579.5</v>
       </c>
       <c r="V2">
-        <v>0.4670019040179662</v>
+        <v>0.474997666241404</v>
       </c>
       <c r="W2">
-        <v>0.09119694172038922</v>
+        <v>0.09106491112361112</v>
       </c>
       <c r="X2">
-        <v>0.0655051857793672</v>
+        <v>0.1025872635337169</v>
       </c>
       <c r="Y2">
-        <v>0.02569175594102202</v>
+        <v>-0.0115223524101058</v>
       </c>
       <c r="Z2">
-        <v>2.55815736474669</v>
+        <v>2.227134138009385</v>
       </c>
       <c r="AA2">
-        <v>0.2069709025069733</v>
+        <v>0.2036543470137887</v>
       </c>
       <c r="AB2">
-        <v>0.05572452345589622</v>
+        <v>0.09151381858568228</v>
       </c>
       <c r="AC2">
-        <v>0.151246379051077</v>
+        <v>0.1121405284281064</v>
       </c>
       <c r="AD2">
-        <v>3872.4</v>
+        <v>2837.6</v>
       </c>
       <c r="AE2">
-        <v>298.0648545258744</v>
+        <v>224.8985355675856</v>
       </c>
       <c r="AF2">
-        <v>4170.464854525874</v>
+        <v>3062.498535567586</v>
       </c>
       <c r="AG2">
-        <v>-612.335145474126</v>
+        <v>-1517.001464432414</v>
       </c>
       <c r="AH2">
-        <v>0.2893751751841248</v>
+        <v>0.2410733090307593</v>
       </c>
       <c r="AI2">
-        <v>0.2028607416062038</v>
+        <v>0.1918053709566528</v>
       </c>
       <c r="AJ2">
-        <v>-0.06359171898342958</v>
+        <v>-0.1867285899833599</v>
       </c>
       <c r="AK2">
-        <v>-0.03881566414180506</v>
+        <v>-0.1332199012508743</v>
       </c>
       <c r="AL2">
-        <v>88.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AM2">
-        <v>88.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AN2">
-        <v>1.491851908926301</v>
+        <v>1.168554132520694</v>
       </c>
       <c r="AO2">
-        <v>26.30890642615558</v>
+        <v>21.62877263581489</v>
       </c>
       <c r="AP2">
-        <v>-0.2359036658605101</v>
+        <v>-0.6247174831908801</v>
       </c>
       <c r="AQ2">
-        <v>26.30890642615558</v>
+        <v>21.62877263581489</v>
       </c>
     </row>
     <row r="3">
@@ -725,103 +725,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0132</v>
+        <v>0.0248</v>
       </c>
       <c r="E3">
-        <v>0.07290000000000001</v>
-      </c>
-      <c r="F3">
-        <v>0.07000000000000001</v>
+        <v>0.0863</v>
       </c>
       <c r="G3">
-        <v>0.1044195292286333</v>
+        <v>0.1654742369543813</v>
       </c>
       <c r="H3">
-        <v>0.1044195292286333</v>
+        <v>0.1654742369543813</v>
       </c>
       <c r="I3">
-        <v>0.1389175203517112</v>
+        <v>0.1532436276118586</v>
       </c>
       <c r="J3">
-        <v>0.1087936747483958</v>
+        <v>0.1181052401269008</v>
       </c>
       <c r="K3">
-        <v>470.4</v>
+        <v>491.4</v>
       </c>
       <c r="L3">
-        <v>0.09895033551399904</v>
+        <v>0.1075155891040367</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>118.7</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03184696286756815</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.2415547415547416</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>118.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03184696286756815</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.2415547415547416</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1974.4</v>
+        <v>2205.6</v>
       </c>
       <c r="V3">
-        <v>0.4926762320648784</v>
+        <v>0.5917578879587895</v>
       </c>
       <c r="W3">
-        <v>0.1119307095607481</v>
+        <v>0.1091199786822996</v>
       </c>
       <c r="X3">
-        <v>0.05684708640616874</v>
+        <v>0.09405423793058922</v>
       </c>
       <c r="Y3">
-        <v>0.05508362315457935</v>
+        <v>0.01506574075171042</v>
       </c>
       <c r="Z3">
-        <v>2.478959169838868</v>
+        <v>2.409838658652325</v>
       </c>
       <c r="AA3">
-        <v>0.2696950776380031</v>
+        <v>0.2846145734472214</v>
       </c>
       <c r="AB3">
-        <v>0.05529239148153069</v>
+        <v>0.09177770797874164</v>
       </c>
       <c r="AC3">
-        <v>0.2144026861564724</v>
+        <v>0.1928368654684797</v>
       </c>
       <c r="AD3">
-        <v>225.8</v>
+        <v>203.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>225.8</v>
+        <v>203.8</v>
       </c>
       <c r="AG3">
-        <v>-1748.6</v>
+        <v>-2001.8</v>
       </c>
       <c r="AH3">
-        <v>0.05333900266931236</v>
+        <v>0.05184431442381074</v>
       </c>
       <c r="AI3">
-        <v>0.04338553175136901</v>
+        <v>0.04464892102092233</v>
       </c>
       <c r="AJ3">
-        <v>-0.774093585373412</v>
+        <v>-1.160194737452185</v>
       </c>
       <c r="AK3">
-        <v>-0.5413454691805208</v>
+        <v>-0.8486158802831829</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.3182522903453136</v>
+        <v>0.264950598023921</v>
       </c>
       <c r="AP3">
-        <v>-2.464552501761804</v>
+        <v>-2.602444097763911</v>
       </c>
     </row>
     <row r="4">
@@ -853,49 +853,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0186</v>
+        <v>-0.0141</v>
       </c>
       <c r="E4">
-        <v>-0.0273</v>
+        <v>0.0239</v>
       </c>
       <c r="F4">
-        <v>0.08740000000000001</v>
+        <v>0.0471</v>
       </c>
       <c r="G4">
-        <v>0.08509238347589493</v>
+        <v>0.08798245832606583</v>
       </c>
       <c r="H4">
-        <v>0.08509238347589493</v>
+        <v>0.08798245832606583</v>
       </c>
       <c r="I4">
-        <v>0.07468421696756464</v>
+        <v>0.07273417351737886</v>
       </c>
       <c r="J4">
-        <v>0.05600622851552645</v>
+        <v>0.05604191323419948</v>
       </c>
       <c r="K4">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="L4">
-        <v>0.03094268490032543</v>
+        <v>0.03563152517878056</v>
       </c>
       <c r="M4">
-        <v>481.821</v>
+        <v>437.1939</v>
       </c>
       <c r="N4">
-        <v>0.07728922040423485</v>
+        <v>0.0739264952062091</v>
       </c>
       <c r="O4">
-        <v>0.692271551724138</v>
+        <v>0.61146</v>
       </c>
       <c r="P4">
-        <v>481.821</v>
+        <v>437.1939</v>
       </c>
       <c r="Q4">
-        <v>0.07728922040423485</v>
+        <v>0.0739264952062091</v>
       </c>
       <c r="R4">
-        <v>0.692271551724138</v>
+        <v>0.61146</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2808.4</v>
+        <v>2373.9</v>
       </c>
       <c r="V4">
-        <v>0.4504972730189284</v>
+        <v>0.401410236899508</v>
       </c>
       <c r="W4">
-        <v>0.07046317388003037</v>
+        <v>0.0730098435649226</v>
       </c>
       <c r="X4">
-        <v>0.07416328515256566</v>
+        <v>0.1111202891368446</v>
       </c>
       <c r="Y4">
-        <v>-0.003700111272535292</v>
+        <v>-0.03811044557192203</v>
       </c>
       <c r="Z4">
-        <v>2.575547955991258</v>
+        <v>2.189327835179655</v>
       </c>
       <c r="AA4">
-        <v>0.1442467273759435</v>
+        <v>0.122694120580356</v>
       </c>
       <c r="AB4">
-        <v>0.05615665543026176</v>
+        <v>0.0912499291926229</v>
       </c>
       <c r="AC4">
-        <v>0.08809007194568171</v>
+        <v>0.03144419138773311</v>
       </c>
       <c r="AD4">
-        <v>3646.6</v>
+        <v>2633.8</v>
       </c>
       <c r="AE4">
-        <v>298.0648545258744</v>
+        <v>224.8985355675856</v>
       </c>
       <c r="AF4">
-        <v>3944.664854525874</v>
+        <v>2858.698535567586</v>
       </c>
       <c r="AG4">
-        <v>1136.264854525874</v>
+        <v>484.7985355675855</v>
       </c>
       <c r="AH4">
-        <v>0.3875424636632874</v>
+        <v>0.3258667912337821</v>
       </c>
       <c r="AI4">
-        <v>0.2569184100382451</v>
+        <v>0.2507146781079342</v>
       </c>
       <c r="AJ4">
-        <v>0.1541687954169145</v>
+        <v>0.07576517832068523</v>
       </c>
       <c r="AK4">
-        <v>0.09057248375809132</v>
+        <v>0.0536976633700901</v>
       </c>
       <c r="AL4">
-        <v>88.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AM4">
-        <v>88.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AN4">
-        <v>1.933305057788145</v>
+        <v>1.587487191851004</v>
       </c>
       <c r="AO4">
-        <v>18.86358511837655</v>
+        <v>14.58249496981891</v>
       </c>
       <c r="AP4">
-        <v>0.6024095294909736</v>
+        <v>0.2922057353791728</v>
       </c>
       <c r="AQ4">
-        <v>18.86358511837655</v>
+        <v>14.58249496981891</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/spain/spain_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_insurance_general.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00535</v>
+        <v>0.004699999999999996</v>
       </c>
       <c r="E2">
-        <v>0.0551</v>
+        <v>0.0274</v>
       </c>
       <c r="F2">
-        <v>0.0471</v>
+        <v>0.123</v>
       </c>
       <c r="G2">
-        <v>0.1023582416690344</v>
+        <v>0.1122420896368822</v>
       </c>
       <c r="H2">
-        <v>0.1023582416690344</v>
+        <v>0.1122420896368822</v>
       </c>
       <c r="I2">
-        <v>0.0876697768756944</v>
+        <v>0.09642553333444531</v>
       </c>
       <c r="J2">
-        <v>0.06755857785238377</v>
+        <v>0.07650414586944508</v>
       </c>
       <c r="K2">
-        <v>1206.4</v>
+        <v>1255.7</v>
       </c>
       <c r="L2">
-        <v>0.04896700085237651</v>
+        <v>0.05236185011592414</v>
       </c>
       <c r="M2">
-        <v>555.8939</v>
+        <v>474.7805</v>
       </c>
       <c r="N2">
-        <v>0.05765876300422152</v>
+        <v>0.0447496630441954</v>
       </c>
       <c r="O2">
-        <v>0.4607873839522547</v>
+        <v>0.3781002628016246</v>
       </c>
       <c r="P2">
-        <v>555.8939</v>
+        <v>474.7805</v>
       </c>
       <c r="Q2">
-        <v>0.05765876300422152</v>
+        <v>0.0447496630441954</v>
       </c>
       <c r="R2">
-        <v>0.4607873839522547</v>
+        <v>0.3781002628016246</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4579.5</v>
+        <v>1425.6</v>
       </c>
       <c r="V2">
-        <v>0.474997666241404</v>
+        <v>0.1343676070011404</v>
       </c>
       <c r="W2">
-        <v>0.09106491112361112</v>
+        <v>0.1175193908920607</v>
       </c>
       <c r="X2">
-        <v>0.1025872635337169</v>
+        <v>0.09044836416182669</v>
       </c>
       <c r="Y2">
-        <v>-0.0115223524101058</v>
+        <v>0.027071026730234</v>
       </c>
       <c r="Z2">
-        <v>2.227134138009385</v>
+        <v>3.26799487612766</v>
       </c>
       <c r="AA2">
-        <v>0.2036543470137887</v>
+        <v>0.4213657725047567</v>
       </c>
       <c r="AB2">
-        <v>0.09151381858568228</v>
+        <v>0.08148244787864792</v>
       </c>
       <c r="AC2">
-        <v>0.1121405284281064</v>
+        <v>0.3398833246261088</v>
       </c>
       <c r="AD2">
-        <v>2837.6</v>
+        <v>3327.6</v>
       </c>
       <c r="AE2">
-        <v>224.8985355675856</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>3062.498535567586</v>
+        <v>3327.6</v>
       </c>
       <c r="AG2">
-        <v>-1517.001464432414</v>
+        <v>1902</v>
       </c>
       <c r="AH2">
-        <v>0.2410733090307593</v>
+        <v>0.2387549955873806</v>
       </c>
       <c r="AI2">
-        <v>0.1918053709566528</v>
+        <v>0.1830191896247326</v>
       </c>
       <c r="AJ2">
-        <v>-0.1867285899833599</v>
+        <v>0.1520177114221089</v>
       </c>
       <c r="AK2">
-        <v>-0.1332199012508743</v>
+        <v>0.1135109005078748</v>
       </c>
       <c r="AL2">
-        <v>99.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="AM2">
-        <v>99.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="AN2">
-        <v>1.168554132520694</v>
+        <v>1.319742999920679</v>
       </c>
       <c r="AO2">
-        <v>21.62877263581489</v>
+        <v>22.62622309197652</v>
       </c>
       <c r="AP2">
-        <v>-0.6247174831908801</v>
+        <v>0.7543428254144525</v>
       </c>
       <c r="AQ2">
-        <v>21.62877263581489</v>
+        <v>22.62622309197652</v>
       </c>
     </row>
     <row r="3">
@@ -725,103 +725,100 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0248</v>
+        <v>0.0464</v>
       </c>
       <c r="E3">
-        <v>0.0863</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1654742369543813</v>
+        <v>0.1838926174496644</v>
       </c>
       <c r="H3">
-        <v>0.1654742369543813</v>
+        <v>0.1838926174496644</v>
       </c>
       <c r="I3">
-        <v>0.1532436276118586</v>
+        <v>0.1890283046396265</v>
       </c>
       <c r="J3">
-        <v>0.1181052401269008</v>
+        <v>0.1453530059243362</v>
       </c>
       <c r="K3">
-        <v>491.4</v>
+        <v>557.2</v>
       </c>
       <c r="L3">
-        <v>0.1075155891040367</v>
+        <v>0.1083941250851085</v>
       </c>
       <c r="M3">
-        <v>118.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03184696286756815</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.2415547415547416</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>118.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03184696286756815</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2415547415547416</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>2205.6</v>
+        <v>1425.6</v>
       </c>
       <c r="V3">
-        <v>0.5917578879587895</v>
+        <v>0.3536503683858004</v>
       </c>
       <c r="W3">
-        <v>0.1091199786822996</v>
+        <v>0.1412098634025191</v>
       </c>
       <c r="X3">
-        <v>0.09405423793058922</v>
+        <v>0.08338608907010953</v>
       </c>
       <c r="Y3">
-        <v>0.01506574075171042</v>
+        <v>0.05782377433240957</v>
       </c>
       <c r="Z3">
-        <v>2.409838658652325</v>
+        <v>4.584410951574066</v>
       </c>
       <c r="AA3">
-        <v>0.2846145734472214</v>
+        <v>0.666357912203737</v>
       </c>
       <c r="AB3">
-        <v>0.09177770797874164</v>
+        <v>0.08187149019140481</v>
       </c>
       <c r="AC3">
-        <v>0.1928368654684797</v>
+        <v>0.5844864220123321</v>
       </c>
       <c r="AD3">
-        <v>203.8</v>
+        <v>174.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>203.8</v>
+        <v>174.3</v>
       </c>
       <c r="AG3">
-        <v>-2001.8</v>
+        <v>-1251.3</v>
       </c>
       <c r="AH3">
-        <v>0.05184431442381074</v>
+        <v>0.04144671137109431</v>
       </c>
       <c r="AI3">
-        <v>0.04464892102092233</v>
+        <v>0.03371242891957758</v>
       </c>
       <c r="AJ3">
-        <v>-1.160194737452185</v>
+        <v>-0.4501402978631556</v>
       </c>
       <c r="AK3">
-        <v>-0.8486158802831829</v>
+        <v>-0.334161192116648</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.264950598023921</v>
+        <v>0.1724376731301939</v>
       </c>
       <c r="AP3">
-        <v>-2.602444097763911</v>
+        <v>-1.23793035219628</v>
       </c>
     </row>
     <row r="4">
@@ -853,49 +850,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0141</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="E4">
-        <v>0.0239</v>
+        <v>-0.0341</v>
       </c>
       <c r="F4">
-        <v>0.0471</v>
+        <v>0.123</v>
       </c>
       <c r="G4">
-        <v>0.08798245832606583</v>
+        <v>0.09269294665272522</v>
       </c>
       <c r="H4">
-        <v>0.08798245832606583</v>
+        <v>0.09269294665272522</v>
       </c>
       <c r="I4">
-        <v>0.07273417351737886</v>
+        <v>0.07115977644142733</v>
       </c>
       <c r="J4">
-        <v>0.05604191323419948</v>
+        <v>0.05819832797031067</v>
       </c>
       <c r="K4">
-        <v>715</v>
+        <v>698.5</v>
       </c>
       <c r="L4">
-        <v>0.03563152517878056</v>
+        <v>0.03707399406603788</v>
       </c>
       <c r="M4">
-        <v>437.1939</v>
+        <v>474.7805</v>
       </c>
       <c r="N4">
-        <v>0.0739264952062091</v>
+        <v>0.07217044659958045</v>
       </c>
       <c r="O4">
-        <v>0.61146</v>
+        <v>0.6797143879742304</v>
       </c>
       <c r="P4">
-        <v>437.1939</v>
+        <v>474.7805</v>
       </c>
       <c r="Q4">
-        <v>0.0739264952062091</v>
+        <v>0.07217044659958045</v>
       </c>
       <c r="R4">
-        <v>0.61146</v>
+        <v>0.6797143879742304</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2373.9</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.401410236899508</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.0730098435649226</v>
+        <v>0.09382891838160229</v>
       </c>
       <c r="X4">
-        <v>0.1111202891368446</v>
+        <v>0.09751063925354386</v>
       </c>
       <c r="Y4">
-        <v>-0.03811044557192203</v>
+        <v>-0.003681720871941574</v>
       </c>
       <c r="Z4">
-        <v>2.189327835179655</v>
+        <v>3.030561855587189</v>
       </c>
       <c r="AA4">
-        <v>0.122694120580356</v>
+        <v>0.1763736328057765</v>
       </c>
       <c r="AB4">
-        <v>0.0912499291926229</v>
+        <v>0.08109340556589102</v>
       </c>
       <c r="AC4">
-        <v>0.03144419138773311</v>
+        <v>0.09528022723988548</v>
       </c>
       <c r="AD4">
-        <v>2633.8</v>
+        <v>3153.3</v>
       </c>
       <c r="AE4">
-        <v>224.8985355675856</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2858.698535567586</v>
+        <v>3153.3</v>
       </c>
       <c r="AG4">
-        <v>484.7985355675855</v>
+        <v>3153.3</v>
       </c>
       <c r="AH4">
-        <v>0.3258667912337821</v>
+        <v>0.3240168928986117</v>
       </c>
       <c r="AI4">
-        <v>0.2507146781079342</v>
+        <v>0.2423471544403028</v>
       </c>
       <c r="AJ4">
-        <v>0.07576517832068523</v>
+        <v>0.3240168928986117</v>
       </c>
       <c r="AK4">
-        <v>0.0536976633700901</v>
+        <v>0.2423471544403028</v>
       </c>
       <c r="AL4">
-        <v>99.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="AM4">
-        <v>99.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="AN4">
-        <v>1.587487191851004</v>
+        <v>2.087448695882431</v>
       </c>
       <c r="AO4">
-        <v>14.58249496981891</v>
+        <v>13.11839530332681</v>
       </c>
       <c r="AP4">
-        <v>0.2922057353791728</v>
+        <v>2.087448695882431</v>
       </c>
       <c r="AQ4">
-        <v>14.58249496981891</v>
+        <v>13.11839530332681</v>
       </c>
     </row>
   </sheetData>
